--- a/PFP-C/Input data and Generated Schedule/85.xlsx
+++ b/PFP-C/Input data and Generated Schedule/85.xlsx
@@ -31945,7 +31945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31970,7 +31970,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -31980,7 +31980,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -31990,11 +31990,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>41.79150000000002</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -42374,7 +42494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42410,25 +42530,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -42461,18 +42576,15 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>252.6366366366366</v>
       </c>
       <c r="I2" t="n">
-        <v>252.6366366366366</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -42505,18 +42617,15 @@
         <v>5.868055555555557</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>253.2372372372372</v>
       </c>
       <c r="I3" t="n">
-        <v>253.2372372372372</v>
+        <v>2.537537537537538</v>
       </c>
       <c r="J3" t="n">
-        <v>2.537537537537538</v>
-      </c>
-      <c r="K3" t="n">
         <v>1.002039654681719</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -42549,18 +42658,15 @@
         <v>6.725663716814152</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>305.4512012012012</v>
       </c>
       <c r="I4" t="n">
-        <v>305.4512012012012</v>
+        <v>3.42342342342342</v>
       </c>
       <c r="J4" t="n">
-        <v>3.42342342342342</v>
-      </c>
-      <c r="K4" t="n">
         <v>1.12077589152069</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42593,18 +42699,15 @@
         <v>4.692982456140341</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>214.2432432432432</v>
       </c>
       <c r="I5" t="n">
-        <v>214.2432432432432</v>
+        <v>1.606606606606603</v>
       </c>
       <c r="J5" t="n">
-        <v>1.606606606606603</v>
-      </c>
-      <c r="K5" t="n">
         <v>0.7498983782571504</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -42637,18 +42740,15 @@
         <v>6.180555555555538</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>244.2282282282282</v>
       </c>
       <c r="I6" t="n">
-        <v>244.2282282282282</v>
+        <v>2.672672672672665</v>
       </c>
       <c r="J6" t="n">
-        <v>2.672672672672665</v>
-      </c>
-      <c r="K6" t="n">
         <v>1.094334054692108</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -42681,18 +42781,15 @@
         <v>8.908554572271374</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>280.8265765765766</v>
       </c>
       <c r="I7" t="n">
-        <v>280.8265765765766</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J7" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K7" t="n">
         <v>1.614709900256908</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42725,18 +42822,15 @@
         <v>6.319999999999997</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>429.0540540540541</v>
       </c>
       <c r="I8" t="n">
-        <v>429.0540540540541</v>
+        <v>4.744744744744742</v>
       </c>
       <c r="J8" t="n">
-        <v>4.744744744744742</v>
-      </c>
-      <c r="K8" t="n">
         <v>1.10586176727909</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42769,18 +42863,15 @@
         <v>4.594594594594581</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>318.6411411411411</v>
       </c>
       <c r="I9" t="n">
-        <v>318.6411411411411</v>
+        <v>2.552552552552545</v>
       </c>
       <c r="J9" t="n">
-        <v>2.552552552552545</v>
-      </c>
-      <c r="K9" t="n">
         <v>0.8010743821124778</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -42813,18 +42904,15 @@
         <v>8.171091445427706</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>310.256006006006</v>
       </c>
       <c r="I10" t="n">
-        <v>310.256006006006</v>
+        <v>4.159159159159147</v>
       </c>
       <c r="J10" t="n">
-        <v>4.159159159159147</v>
-      </c>
-      <c r="K10" t="n">
         <v>1.340557178151334</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -42857,18 +42945,15 @@
         <v>4.309392265193361</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>338.466966966967</v>
       </c>
       <c r="I11" t="n">
-        <v>338.466966966967</v>
+        <v>2.342342342342338</v>
       </c>
       <c r="J11" t="n">
-        <v>2.342342342342338</v>
-      </c>
-      <c r="K11" t="n">
         <v>0.6920445925143829</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42901,18 +42986,15 @@
         <v>2.052980132450326</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>253.527027027027</v>
       </c>
       <c r="I12" t="n">
-        <v>253.527027027027</v>
+        <v>0.9309309309309284</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9309309309309284</v>
-      </c>
-      <c r="K12" t="n">
         <v>0.3671919881077166</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -42945,18 +43027,15 @@
         <v>5.655526992287911</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>324.3325825825826</v>
       </c>
       <c r="I13" t="n">
-        <v>324.3325825825826</v>
+        <v>3.303303303303299</v>
       </c>
       <c r="J13" t="n">
-        <v>3.303303303303299</v>
-      </c>
-      <c r="K13" t="n">
         <v>1.018492584679556</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -42989,18 +43068,15 @@
         <v>7.004504504504484</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>378.045045045045</v>
       </c>
       <c r="I14" t="n">
-        <v>378.045045045045</v>
+        <v>4.669669669669655</v>
       </c>
       <c r="J14" t="n">
-        <v>4.669669669669655</v>
-      </c>
-      <c r="K14" t="n">
         <v>1.235215149854233</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43033,18 +43109,15 @@
         <v>7.991360691144692</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>418.5713213213213</v>
       </c>
       <c r="I15" t="n">
-        <v>418.5713213213213</v>
+        <v>5.555555555555543</v>
       </c>
       <c r="J15" t="n">
-        <v>5.555555555555543</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.327266172469268</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43077,18 +43150,15 @@
         <v>7.5689223057644</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>351.0518018018018</v>
       </c>
       <c r="I16" t="n">
-        <v>351.0518018018018</v>
+        <v>4.534534534534528</v>
       </c>
       <c r="J16" t="n">
-        <v>4.534534534534528</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.291699547263584</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43121,18 +43191,15 @@
         <v>4.812030075187952</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>350.7515015015015</v>
       </c>
       <c r="I17" t="n">
-        <v>350.7515015015015</v>
+        <v>2.882882882882872</v>
       </c>
       <c r="J17" t="n">
-        <v>2.882882882882872</v>
-      </c>
-      <c r="K17" t="n">
         <v>0.8219160489810563</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43165,18 +43232,15 @@
         <v>2.582159624413153</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>372.6531531531531</v>
       </c>
       <c r="I18" t="n">
-        <v>372.6531531531531</v>
+        <v>1.651651651651656</v>
       </c>
       <c r="J18" t="n">
-        <v>1.651651651651656</v>
-      </c>
-      <c r="K18" t="n">
         <v>0.4432141893008107</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43209,18 +43273,15 @@
         <v>6.291079812206559</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>366.6471471471472</v>
       </c>
       <c r="I19" t="n">
-        <v>366.6471471471472</v>
+        <v>4.024024024024014</v>
       </c>
       <c r="J19" t="n">
-        <v>4.024024024024014</v>
-      </c>
-      <c r="K19" t="n">
         <v>1.09751952397138</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43253,18 +43314,15 @@
         <v>3.633633633633621</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>300.9512012012012</v>
       </c>
       <c r="I20" t="n">
-        <v>300.9512012012012</v>
+        <v>1.81681681681681</v>
       </c>
       <c r="J20" t="n">
-        <v>1.81681681681681</v>
-      </c>
-      <c r="K20" t="n">
         <v>0.6036914986766161</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43297,18 +43355,15 @@
         <v>5.30701754385965</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>204.933933933934</v>
       </c>
       <c r="I21" t="n">
-        <v>204.933933933934</v>
+        <v>1.816816816816817</v>
       </c>
       <c r="J21" t="n">
-        <v>1.816816816816817</v>
-      </c>
-      <c r="K21" t="n">
         <v>0.8865378134021069</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43341,18 +43396,15 @@
         <v>4.824561403508767</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>184.8138138138138</v>
       </c>
       <c r="I22" t="n">
-        <v>184.8138138138138</v>
+        <v>1.65165165165165</v>
       </c>
       <c r="J22" t="n">
-        <v>1.65165165165165</v>
-      </c>
-      <c r="K22" t="n">
         <v>0.8936840907983027</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43385,18 +43437,15 @@
         <v>6.760563380281676</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>359.7402402402403</v>
       </c>
       <c r="I23" t="n">
-        <v>359.7402402402403</v>
+        <v>4.324324324324315</v>
       </c>
       <c r="J23" t="n">
-        <v>4.324324324324315</v>
-      </c>
-      <c r="K23" t="n">
         <v>1.202068559646389</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43429,18 +43478,15 @@
         <v>7.549668874172177</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>269.4429429429429</v>
       </c>
       <c r="I24" t="n">
-        <v>269.4429429429429</v>
+        <v>3.42342342342342</v>
       </c>
       <c r="J24" t="n">
-        <v>3.42342342342342</v>
-      </c>
-      <c r="K24" t="n">
         <v>1.270555979693393</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43473,18 +43519,15 @@
         <v>6.940874035989718</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>337.2454954954955</v>
       </c>
       <c r="I25" t="n">
-        <v>337.2454954954955</v>
+        <v>4.054054054054054</v>
       </c>
       <c r="J25" t="n">
-        <v>4.054054054054054</v>
-      </c>
-      <c r="K25" t="n">
         <v>1.202107695492764</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43517,18 +43560,15 @@
         <v>5.690607734806616</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>337.2657657657658</v>
       </c>
       <c r="I26" t="n">
-        <v>337.2657657657658</v>
+        <v>3.093093093093085</v>
       </c>
       <c r="J26" t="n">
-        <v>3.093093093093085</v>
-      </c>
-      <c r="K26" t="n">
         <v>0.9171085259929013</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -43545,7 +43585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43571,20 +43611,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -43617,9 +43652,6 @@
       <c r="H2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -43640,15 +43672,12 @@
         <v>5.617455236230573</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>310.2805705705705</v>
       </c>
       <c r="G3" t="n">
-        <v>310.2805705705705</v>
+        <v>3.052252252252247</v>
       </c>
       <c r="H3" t="n">
-        <v>3.052252252252247</v>
-      </c>
-      <c r="I3" t="n">
         <v>0.9639826067118374</v>
       </c>
     </row>
@@ -43671,15 +43700,12 @@
         <v>2.046024793562692</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>64.10486510743279</v>
       </c>
       <c r="G4" t="n">
-        <v>64.10486510743279</v>
+        <v>1.37456783536911</v>
       </c>
       <c r="H4" t="n">
-        <v>1.37456783536911</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.3556449370269119</v>
       </c>
     </row>
@@ -43702,15 +43728,12 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>184.8138138138138</v>
       </c>
       <c r="G5" t="n">
-        <v>184.8138138138138</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -43733,15 +43756,12 @@
         <v>4.692982456140341</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>253.527027027027</v>
       </c>
       <c r="G6" t="n">
-        <v>253.527027027027</v>
+        <v>1.816816816816817</v>
       </c>
       <c r="H6" t="n">
-        <v>1.816816816816817</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.8010743821124778</v>
       </c>
     </row>
@@ -43764,15 +43784,12 @@
         <v>5.868055555555557</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>318.6411411411411</v>
       </c>
       <c r="G7" t="n">
-        <v>318.6411411411411</v>
+        <v>3.093093093093085</v>
       </c>
       <c r="H7" t="n">
-        <v>3.093093093093085</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.018492584679556</v>
       </c>
     </row>
@@ -43795,15 +43812,12 @@
         <v>6.940874035989718</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>351.0518018018018</v>
       </c>
       <c r="G8" t="n">
-        <v>351.0518018018018</v>
+        <v>4.159159159159147</v>
       </c>
       <c r="H8" t="n">
-        <v>4.159159159159147</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.202107695492764</v>
       </c>
     </row>
@@ -43826,15 +43840,12 @@
         <v>8.908554572271374</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>429.0540540540541</v>
       </c>
       <c r="G9" t="n">
-        <v>429.0540540540541</v>
+        <v>5.555555555555543</v>
       </c>
       <c r="H9" t="n">
-        <v>5.555555555555543</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.614709900256908</v>
       </c>
     </row>
